--- a/Assets/Data/Map0010.xlsx
+++ b/Assets/Data/Map0010.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F5A66B-E9D1-44A8-867C-F1F94EE2DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Map" sheetId="1" r:id="rId1"/>
@@ -19,18 +13,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -38,39 +21,30 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="17">
   <si>
     <t>_</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>StageId</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>InitX</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>InitY</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>UnitType</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>*</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>InitTeamId</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Rate</t>
@@ -89,11 +63,9 @@
   </si>
   <si>
     <t>MoveType</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>MoveParam</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Seek=-1でステージ開始時に入手</t>
@@ -102,8 +74,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,27 +93,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -143,9 +443,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -160,28 +702,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Stages"/>
       <sheetName val="StageEvents"/>
@@ -599,22 +1182,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="2.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="40" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="2.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.27272727272727" customWidth="1"/>
+    <col min="2" max="10" width="2.27272727272727" customWidth="1"/>
+    <col min="11" max="40" width="3.27272727272727" customWidth="1"/>
+    <col min="41" max="41" width="2.81818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +1322,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:41">
       <c r="A2">
         <v>1</v>
       </c>
@@ -864,7 +1447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41">
       <c r="A3">
         <v>2</v>
       </c>
@@ -989,7 +1572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:41">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1114,7 +1697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1239,7 +1822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1364,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1489,7 +2072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1614,7 +2197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1739,7 +2322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1864,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1989,7 +2572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2114,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2239,7 +2822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2364,7 +2947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2489,7 +3072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2614,7 +3197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2739,7 +3322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2864,7 +3447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2989,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:41">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3114,7 +3697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:41">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3239,7 +3822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3364,7 +3947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3489,7 +4072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3614,7 +4197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3739,7 +4322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3864,7 +4447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:41">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3989,7 +4572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:41">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4114,7 +4697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:41">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4239,7 +4822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:41">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4364,7 +4947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:41">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4489,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:41">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4614,7 +5197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:41">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4739,7 +5322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:41">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4864,7 +5447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:41">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4989,7 +5572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:41">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5114,7 +5697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:41">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5239,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:41">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5360,7 +5943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:41">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5469,7 +6052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:41">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5588,7 +6171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5714,18 +6297,19 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30ECAC24-1D32-444C-8B2B-B82C8B7A4C87}">
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5769,7 +6353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -5817,7 +6401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -5862,7 +6446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -5907,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -5952,7 +6536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -5997,7 +6581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -6042,8 +6626,98 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>1060</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>70</v>
+      </c>
+      <c r="F8" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E8,[1]Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>1070</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E9,[1]Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Map0010.xlsx
+++ b/Assets/Data/Map0010.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Map" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="17">
   <si>
     <t>_</t>
   </si>
@@ -76,9 +76,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -97,8 +97,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -113,14 +167,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -135,89 +220,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -225,17 +227,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +250,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,13 +262,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -292,7 +292,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,31 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,7 +352,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -352,25 +376,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,43 +394,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,17 +446,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -501,21 +494,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -533,11 +511,33 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,145 +549,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1454,81 +1454,31 @@
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
       <c r="AB3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1579,81 +1529,31 @@
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
       <c r="AB4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1704,81 +1604,31 @@
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
       <c r="AB5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1829,81 +1679,31 @@
       <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
       <c r="AB6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1954,81 +1754,31 @@
       <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
       <c r="AB7" s="2" t="s">
         <v>1</v>
       </c>
@@ -2079,81 +1829,31 @@
       <c r="B8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
       <c r="AB8" s="2" t="s">
         <v>1</v>
       </c>
@@ -2204,81 +1904,31 @@
       <c r="B9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
       <c r="AB9" s="2" t="s">
         <v>1</v>
       </c>
@@ -2329,81 +1979,31 @@
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
       <c r="AB10" s="2" t="s">
         <v>1</v>
       </c>
@@ -2454,81 +2054,31 @@
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
         <v>1</v>
       </c>
@@ -2579,81 +2129,31 @@
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
       <c r="AB12" s="2" t="s">
         <v>1</v>
       </c>
@@ -2704,81 +2204,31 @@
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
       <c r="AB13" s="2" t="s">
         <v>1</v>
       </c>
@@ -2859,81 +2309,31 @@
       <c r="L14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK14" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="2"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="2"/>
+      <c r="AI14" s="2"/>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="2"/>
       <c r="AL14" s="2" t="s">
         <v>1</v>
       </c>
@@ -2984,81 +2384,31 @@
       <c r="L15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK15" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
       <c r="AL15" s="2" t="s">
         <v>1</v>
       </c>
@@ -3109,81 +2459,31 @@
       <c r="L16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK16" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
       <c r="AL16" s="2" t="s">
         <v>1</v>
       </c>
@@ -3234,81 +2534,31 @@
       <c r="L17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK17" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="2"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="2"/>
       <c r="AL17" s="2" t="s">
         <v>1</v>
       </c>
@@ -3359,81 +2609,31 @@
       <c r="L18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK18" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
       <c r="AL18" s="2" t="s">
         <v>1</v>
       </c>
@@ -3484,81 +2684,31 @@
       <c r="L19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
       <c r="AL19" s="2" t="s">
         <v>1</v>
       </c>
@@ -3609,81 +2759,31 @@
       <c r="L20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK20" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="2"/>
       <c r="AL20" s="2" t="s">
         <v>1</v>
       </c>
@@ -3734,81 +2834,31 @@
       <c r="L21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK21" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21" s="2"/>
+      <c r="AK21" s="2"/>
       <c r="AL21" s="2" t="s">
         <v>1</v>
       </c>
@@ -3859,81 +2909,31 @@
       <c r="L22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK22" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="2"/>
+      <c r="AG22" s="2"/>
+      <c r="AH22" s="2"/>
+      <c r="AI22" s="2"/>
+      <c r="AJ22" s="2"/>
+      <c r="AK22" s="2"/>
       <c r="AL22" s="2" t="s">
         <v>1</v>
       </c>
@@ -3984,81 +2984,31 @@
       <c r="L23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK23" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
       <c r="AL23" s="2" t="s">
         <v>1</v>
       </c>
@@ -4109,81 +3059,31 @@
       <c r="L24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK24" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
       <c r="AL24" s="2" t="s">
         <v>1</v>
       </c>
@@ -4243,81 +3143,31 @@
       <c r="O25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN25" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="2"/>
+      <c r="AL25" s="2"/>
+      <c r="AM25" s="2"/>
+      <c r="AN25" s="2"/>
       <c r="AO25" s="2" t="s">
         <v>1</v>
       </c>
@@ -4368,81 +3218,31 @@
       <c r="O26" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN26" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="2"/>
+      <c r="AL26" s="2"/>
+      <c r="AM26" s="2"/>
+      <c r="AN26" s="2"/>
       <c r="AO26" s="2" t="s">
         <v>1</v>
       </c>
@@ -4493,81 +3293,31 @@
       <c r="O27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN27" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+      <c r="AL27" s="2"/>
+      <c r="AM27" s="2"/>
+      <c r="AN27" s="2"/>
       <c r="AO27" s="2" t="s">
         <v>1</v>
       </c>
@@ -4618,81 +3368,31 @@
       <c r="O28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN28" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
+      <c r="AM28" s="2"/>
+      <c r="AN28" s="2"/>
       <c r="AO28" s="2" t="s">
         <v>1</v>
       </c>
@@ -4743,81 +3443,31 @@
       <c r="O29" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN29" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+      <c r="AL29" s="2"/>
+      <c r="AM29" s="2"/>
+      <c r="AN29" s="2"/>
       <c r="AO29" s="2" t="s">
         <v>1</v>
       </c>
@@ -4868,81 +3518,31 @@
       <c r="O30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
+      <c r="AI30" s="2"/>
+      <c r="AJ30" s="2"/>
+      <c r="AK30" s="2"/>
+      <c r="AL30" s="2"/>
+      <c r="AM30" s="2"/>
+      <c r="AN30" s="2"/>
       <c r="AO30" s="2" t="s">
         <v>1</v>
       </c>
@@ -4993,81 +3593,31 @@
       <c r="O31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN31" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AH31" s="2"/>
+      <c r="AI31" s="2"/>
+      <c r="AJ31" s="2"/>
+      <c r="AK31" s="2"/>
+      <c r="AL31" s="2"/>
+      <c r="AM31" s="2"/>
+      <c r="AN31" s="2"/>
       <c r="AO31" s="2" t="s">
         <v>1</v>
       </c>
@@ -5118,81 +3668,31 @@
       <c r="O32" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN32" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="2"/>
+      <c r="AG32" s="2"/>
+      <c r="AH32" s="2"/>
+      <c r="AI32" s="2"/>
+      <c r="AJ32" s="2"/>
+      <c r="AK32" s="2"/>
+      <c r="AL32" s="2"/>
+      <c r="AM32" s="2"/>
+      <c r="AN32" s="2"/>
       <c r="AO32" s="2" t="s">
         <v>1</v>
       </c>
@@ -5243,81 +3743,31 @@
       <c r="O33" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN33" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="2"/>
+      <c r="AE33" s="2"/>
+      <c r="AF33" s="2"/>
+      <c r="AG33" s="2"/>
+      <c r="AH33" s="2"/>
+      <c r="AI33" s="2"/>
+      <c r="AJ33" s="2"/>
+      <c r="AK33" s="2"/>
+      <c r="AL33" s="2"/>
+      <c r="AM33" s="2"/>
+      <c r="AN33" s="2"/>
       <c r="AO33" s="2" t="s">
         <v>1</v>
       </c>
@@ -5368,81 +3818,31 @@
       <c r="O34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN34" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
+      <c r="AG34" s="2"/>
+      <c r="AH34" s="2"/>
+      <c r="AI34" s="2"/>
+      <c r="AJ34" s="2"/>
+      <c r="AK34" s="2"/>
+      <c r="AL34" s="2"/>
+      <c r="AM34" s="2"/>
+      <c r="AN34" s="2"/>
       <c r="AO34" s="2" t="s">
         <v>1</v>
       </c>
@@ -5493,81 +3893,31 @@
       <c r="O35" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN35" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="2"/>
+      <c r="AE35" s="2"/>
+      <c r="AF35" s="2"/>
+      <c r="AG35" s="2"/>
+      <c r="AH35" s="2"/>
+      <c r="AI35" s="2"/>
+      <c r="AJ35" s="2"/>
+      <c r="AK35" s="2"/>
+      <c r="AL35" s="2"/>
+      <c r="AM35" s="2"/>
+      <c r="AN35" s="2"/>
       <c r="AO35" s="2" t="s">
         <v>1</v>
       </c>

--- a/Assets/Data/Map0010.xlsx
+++ b/Assets/Data/Map0010.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Map" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="18">
   <si>
     <t>_</t>
   </si>
@@ -70,6 +70,9 @@
   <si>
     <t>Seek=-1でステージ開始時に入手</t>
   </si>
+  <si>
+    <t>Param1=マップ開放フラグ Param2でマップId</t>
+  </si>
 </sst>
 </file>
 
@@ -77,9 +80,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -94,6 +97,111 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -113,51 +221,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -166,69 +229,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,7 +253,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,19 +295,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,13 +337,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,25 +409,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,97 +433,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,11 +449,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -485,15 +486,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -518,6 +510,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -532,15 +544,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -549,145 +552,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1386,9 +1389,7 @@
       <c r="U2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="V2" s="2"/>
       <c r="W2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1454,31 +1455,79 @@
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
+      <c r="W3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1529,31 +1578,79 @@
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
+      <c r="W4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1604,31 +1701,79 @@
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
+      <c r="W5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1679,31 +1824,81 @@
       <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1754,31 +1949,81 @@
       <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1829,31 +2074,81 @@
       <c r="B8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB8" s="2" t="s">
         <v>1</v>
       </c>
@@ -1904,31 +2199,81 @@
       <c r="B9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB9" s="2" t="s">
         <v>1</v>
       </c>
@@ -1979,31 +2324,81 @@
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB10" s="2" t="s">
         <v>1</v>
       </c>
@@ -2054,31 +2449,81 @@
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB11" s="2" t="s">
         <v>1</v>
       </c>
@@ -2129,31 +2574,81 @@
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB12" s="2" t="s">
         <v>1</v>
       </c>
@@ -2204,31 +2699,81 @@
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AB13" s="2" t="s">
         <v>1</v>
       </c>
@@ -2309,31 +2854,81 @@
       <c r="L14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL14" s="2" t="s">
         <v>1</v>
       </c>
@@ -2384,31 +2979,81 @@
       <c r="L15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="2"/>
-      <c r="AE15" s="2"/>
-      <c r="AF15" s="2"/>
-      <c r="AG15" s="2"/>
-      <c r="AH15" s="2"/>
-      <c r="AI15" s="2"/>
-      <c r="AJ15" s="2"/>
-      <c r="AK15" s="2"/>
+      <c r="M15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2459,31 +3104,81 @@
       <c r="L16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="2"/>
-      <c r="AE16" s="2"/>
-      <c r="AF16" s="2"/>
-      <c r="AG16" s="2"/>
-      <c r="AH16" s="2"/>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL16" s="2" t="s">
         <v>1</v>
       </c>
@@ -2534,31 +3229,81 @@
       <c r="L17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
-      <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-      <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
+      <c r="M17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL17" s="2" t="s">
         <v>1</v>
       </c>
@@ -2609,31 +3354,81 @@
       <c r="L18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
-      <c r="AD18" s="2"/>
-      <c r="AE18" s="2"/>
-      <c r="AF18" s="2"/>
-      <c r="AG18" s="2"/>
-      <c r="AH18" s="2"/>
-      <c r="AI18" s="2"/>
-      <c r="AJ18" s="2"/>
-      <c r="AK18" s="2"/>
+      <c r="M18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL18" s="2" t="s">
         <v>1</v>
       </c>
@@ -2684,31 +3479,81 @@
       <c r="L19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
+      <c r="M19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL19" s="2" t="s">
         <v>1</v>
       </c>
@@ -2759,31 +3604,81 @@
       <c r="L20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
-      <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-      <c r="AG20" s="2"/>
-      <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
+      <c r="M20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL20" s="2" t="s">
         <v>1</v>
       </c>
@@ -2834,31 +3729,81 @@
       <c r="L21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
-      <c r="AG21" s="2"/>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
+      <c r="M21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL21" s="2" t="s">
         <v>1</v>
       </c>
@@ -2909,31 +3854,81 @@
       <c r="L22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-      <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="2"/>
-      <c r="AG22" s="2"/>
-      <c r="AH22" s="2"/>
-      <c r="AI22" s="2"/>
-      <c r="AJ22" s="2"/>
-      <c r="AK22" s="2"/>
+      <c r="M22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK22" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL22" s="2" t="s">
         <v>1</v>
       </c>
@@ -2984,31 +3979,81 @@
       <c r="L23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-      <c r="AC23" s="2"/>
-      <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-      <c r="AF23" s="2"/>
-      <c r="AG23" s="2"/>
-      <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
+      <c r="M23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK23" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL23" s="2" t="s">
         <v>1</v>
       </c>
@@ -3059,31 +4104,81 @@
       <c r="L24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
+      <c r="M24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL24" s="2" t="s">
         <v>1</v>
       </c>
@@ -3143,31 +4238,81 @@
       <c r="O25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-      <c r="AD25" s="2"/>
-      <c r="AE25" s="2"/>
-      <c r="AF25" s="2"/>
-      <c r="AG25" s="2"/>
-      <c r="AH25" s="2"/>
-      <c r="AI25" s="2"/>
-      <c r="AJ25" s="2"/>
-      <c r="AK25" s="2"/>
-      <c r="AL25" s="2"/>
-      <c r="AM25" s="2"/>
-      <c r="AN25" s="2"/>
+      <c r="P25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO25" s="2" t="s">
         <v>1</v>
       </c>
@@ -3218,31 +4363,81 @@
       <c r="O26" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-      <c r="AC26" s="2"/>
-      <c r="AD26" s="2"/>
-      <c r="AE26" s="2"/>
-      <c r="AF26" s="2"/>
-      <c r="AG26" s="2"/>
-      <c r="AH26" s="2"/>
-      <c r="AI26" s="2"/>
-      <c r="AJ26" s="2"/>
-      <c r="AK26" s="2"/>
-      <c r="AL26" s="2"/>
-      <c r="AM26" s="2"/>
-      <c r="AN26" s="2"/>
+      <c r="P26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO26" s="2" t="s">
         <v>1</v>
       </c>
@@ -3293,31 +4488,81 @@
       <c r="O27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
-      <c r="AC27" s="2"/>
-      <c r="AD27" s="2"/>
-      <c r="AE27" s="2"/>
-      <c r="AF27" s="2"/>
-      <c r="AG27" s="2"/>
-      <c r="AH27" s="2"/>
-      <c r="AI27" s="2"/>
-      <c r="AJ27" s="2"/>
-      <c r="AK27" s="2"/>
-      <c r="AL27" s="2"/>
-      <c r="AM27" s="2"/>
-      <c r="AN27" s="2"/>
+      <c r="P27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO27" s="2" t="s">
         <v>1</v>
       </c>
@@ -3368,31 +4613,81 @@
       <c r="O28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="2"/>
-      <c r="AC28" s="2"/>
-      <c r="AD28" s="2"/>
-      <c r="AE28" s="2"/>
-      <c r="AF28" s="2"/>
-      <c r="AG28" s="2"/>
-      <c r="AH28" s="2"/>
-      <c r="AI28" s="2"/>
-      <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
-      <c r="AL28" s="2"/>
-      <c r="AM28" s="2"/>
-      <c r="AN28" s="2"/>
+      <c r="P28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO28" s="2" t="s">
         <v>1</v>
       </c>
@@ -3443,31 +4738,81 @@
       <c r="O29" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-      <c r="AD29" s="2"/>
-      <c r="AE29" s="2"/>
-      <c r="AF29" s="2"/>
-      <c r="AG29" s="2"/>
-      <c r="AH29" s="2"/>
-      <c r="AI29" s="2"/>
-      <c r="AJ29" s="2"/>
-      <c r="AK29" s="2"/>
-      <c r="AL29" s="2"/>
-      <c r="AM29" s="2"/>
-      <c r="AN29" s="2"/>
+      <c r="P29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO29" s="2" t="s">
         <v>1</v>
       </c>
@@ -3518,31 +4863,81 @@
       <c r="O30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="2"/>
-      <c r="AA30" s="2"/>
-      <c r="AB30" s="2"/>
-      <c r="AC30" s="2"/>
-      <c r="AD30" s="2"/>
-      <c r="AE30" s="2"/>
-      <c r="AF30" s="2"/>
-      <c r="AG30" s="2"/>
-      <c r="AH30" s="2"/>
-      <c r="AI30" s="2"/>
-      <c r="AJ30" s="2"/>
-      <c r="AK30" s="2"/>
-      <c r="AL30" s="2"/>
-      <c r="AM30" s="2"/>
-      <c r="AN30" s="2"/>
+      <c r="P30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO30" s="2" t="s">
         <v>1</v>
       </c>
@@ -3593,31 +4988,81 @@
       <c r="O31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
-      <c r="Z31" s="2"/>
-      <c r="AA31" s="2"/>
-      <c r="AB31" s="2"/>
-      <c r="AC31" s="2"/>
-      <c r="AD31" s="2"/>
-      <c r="AE31" s="2"/>
-      <c r="AF31" s="2"/>
-      <c r="AG31" s="2"/>
-      <c r="AH31" s="2"/>
-      <c r="AI31" s="2"/>
-      <c r="AJ31" s="2"/>
-      <c r="AK31" s="2"/>
-      <c r="AL31" s="2"/>
-      <c r="AM31" s="2"/>
-      <c r="AN31" s="2"/>
+      <c r="P31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN31" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO31" s="2" t="s">
         <v>1</v>
       </c>
@@ -3668,31 +5113,81 @@
       <c r="O32" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
-      <c r="AC32" s="2"/>
-      <c r="AD32" s="2"/>
-      <c r="AE32" s="2"/>
-      <c r="AF32" s="2"/>
-      <c r="AG32" s="2"/>
-      <c r="AH32" s="2"/>
-      <c r="AI32" s="2"/>
-      <c r="AJ32" s="2"/>
-      <c r="AK32" s="2"/>
-      <c r="AL32" s="2"/>
-      <c r="AM32" s="2"/>
-      <c r="AN32" s="2"/>
+      <c r="P32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO32" s="2" t="s">
         <v>1</v>
       </c>
@@ -3743,31 +5238,81 @@
       <c r="O33" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="2"/>
-      <c r="AA33" s="2"/>
-      <c r="AB33" s="2"/>
-      <c r="AC33" s="2"/>
-      <c r="AD33" s="2"/>
-      <c r="AE33" s="2"/>
-      <c r="AF33" s="2"/>
-      <c r="AG33" s="2"/>
-      <c r="AH33" s="2"/>
-      <c r="AI33" s="2"/>
-      <c r="AJ33" s="2"/>
-      <c r="AK33" s="2"/>
-      <c r="AL33" s="2"/>
-      <c r="AM33" s="2"/>
-      <c r="AN33" s="2"/>
+      <c r="P33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO33" s="2" t="s">
         <v>1</v>
       </c>
@@ -3818,31 +5363,81 @@
       <c r="O34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="2"/>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2"/>
-      <c r="AB34" s="2"/>
-      <c r="AC34" s="2"/>
-      <c r="AD34" s="2"/>
-      <c r="AE34" s="2"/>
-      <c r="AF34" s="2"/>
-      <c r="AG34" s="2"/>
-      <c r="AH34" s="2"/>
-      <c r="AI34" s="2"/>
-      <c r="AJ34" s="2"/>
-      <c r="AK34" s="2"/>
-      <c r="AL34" s="2"/>
-      <c r="AM34" s="2"/>
-      <c r="AN34" s="2"/>
+      <c r="P34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO34" s="2" t="s">
         <v>1</v>
       </c>
@@ -3893,31 +5488,81 @@
       <c r="O35" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
-      <c r="Y35" s="2"/>
-      <c r="Z35" s="2"/>
-      <c r="AA35" s="2"/>
-      <c r="AB35" s="2"/>
-      <c r="AC35" s="2"/>
-      <c r="AD35" s="2"/>
-      <c r="AE35" s="2"/>
-      <c r="AF35" s="2"/>
-      <c r="AG35" s="2"/>
-      <c r="AH35" s="2"/>
-      <c r="AI35" s="2"/>
-      <c r="AJ35" s="2"/>
-      <c r="AK35" s="2"/>
-      <c r="AL35" s="2"/>
-      <c r="AM35" s="2"/>
-      <c r="AN35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN35" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AO35" s="2" t="s">
         <v>1</v>
       </c>
@@ -4263,8 +5908,12 @@
       <c r="AD38" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AE38" s="2"/>
-      <c r="AF38" s="2"/>
+      <c r="AE38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AG38" s="2" t="s">
         <v>1</v>
       </c>
@@ -4384,14 +6033,30 @@
       <c r="AD39" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AE39" s="2"/>
-      <c r="AF39" s="2"/>
-      <c r="AG39" s="2"/>
-      <c r="AH39" s="2"/>
-      <c r="AI39" s="2"/>
-      <c r="AJ39" s="2"/>
-      <c r="AK39" s="2"/>
-      <c r="AL39" s="2"/>
+      <c r="AE39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL39" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AM39" s="2" t="s">
         <v>1</v>
       </c>
@@ -4499,15 +6164,21 @@
       <c r="AF40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AG40" s="2"/>
+      <c r="AG40" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AH40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AI40" s="2"/>
+      <c r="AI40" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AJ40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AK40" s="2"/>
+      <c r="AK40" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL40" s="2" t="s">
         <v>1</v>
       </c>
@@ -4759,10 +6430,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -4796,7 +6467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -4804,17 +6475,17 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F4" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E4,[1]Define!K:K))</f>
-        <v>Gacha</v>
+        <v>Basement</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4839,6 +6510,9 @@
       </c>
       <c r="N4">
         <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4849,17 +6523,17 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>38</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F5" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E5,[1]Define!K:K))</f>
-        <v>Basement</v>
+        <v>Gacha</v>
       </c>
       <c r="G5">
         <v>0</v>

--- a/Assets/Data/Map0010.xlsx
+++ b/Assets/Data/Map0010.xlsx
@@ -79,9 +79,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -107,22 +107,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -135,24 +122,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -166,48 +167,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,6 +191,45 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -230,17 +237,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -259,19 +259,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,91 +313,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +331,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,25 +403,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,13 +421,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,15 +444,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -467,56 +458,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,6 +485,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -552,145 +552,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6327,8 +6327,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="3"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -6494,10 +6494,10 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -6513,231 +6513,6 @@
       </c>
       <c r="O4" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5">
-        <v>1030</v>
-      </c>
-      <c r="B5">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>35</v>
-      </c>
-      <c r="D5">
-        <v>38</v>
-      </c>
-      <c r="E5">
-        <v>90</v>
-      </c>
-      <c r="F5" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E5,[1]Define!K:K))</f>
-        <v>Gacha</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6">
-        <v>1040</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>30</v>
-      </c>
-      <c r="D6">
-        <v>37</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E6,[1]Define!K:K))</f>
-        <v>Battler</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-      <c r="I6">
-        <v>1011</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>1011</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7">
-        <v>1050</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>37</v>
-      </c>
-      <c r="E7">
-        <v>20</v>
-      </c>
-      <c r="F7" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E7,[1]Define!K:K))</f>
-        <v>Basement</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8">
-        <v>1060</v>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>36</v>
-      </c>
-      <c r="D8">
-        <v>38</v>
-      </c>
-      <c r="E8">
-        <v>70</v>
-      </c>
-      <c r="F8" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E8,[1]Define!K:K))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>1000</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9">
-        <v>1070</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>36</v>
-      </c>
-      <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>70</v>
-      </c>
-      <c r="F9" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E9,[1]Define!K:K))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1000</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Map0010.xlsx
+++ b/Assets/Data/Map0010.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="18">
   <si>
     <t>_</t>
   </si>
@@ -79,10 +79,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -101,9 +101,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -116,7 +161,62 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -124,13 +224,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -145,102 +238,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -253,7 +253,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,7 +265,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -277,13 +349,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -295,145 +427,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,6 +444,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -466,7 +475,48 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,58 +539,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,145 +552,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6327,8 +6327,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="3"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -6422,28 +6422,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="B3">
         <v>10</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F3" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E3,[1]Define!K:K))</f>
-        <v>Basement</v>
+        <v>SelectActor</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -6465,27 +6465,30 @@
       </c>
       <c r="N3">
         <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F4" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E4,[1]Define!K:K))</f>
-        <v>Basement</v>
+        <v>SelectActor</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -6494,13 +6497,13 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -6512,6 +6515,243 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>-1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+      <c r="F5" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E5,[1]Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1004</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <v>1000</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>-1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+      <c r="F6" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E6,[1]Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1005</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>70</v>
+      </c>
+      <c r="F7" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E7,[1]Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1006</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>1010</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E8,[1]Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <v>1020</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9" t="str">
+        <f>INDEX([1]Define!L:L,MATCH(E9,[1]Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
         <v>17</v>
       </c>
     </row>
